--- a/www/download/COUNTRY.FIN.WIOD16.xlsx
+++ b/www/download/COUNTRY.FIN.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Finlândia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1.0827197921178</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1.11656989727557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1.0575296108291</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.884016973125884</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.803923144947343</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.803793907242183</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.796431984708506</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.729660707770887</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.67990209409845</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.71694866647548</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0.75431847325941</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.718390804597701</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.778331257783312</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.75295534974776</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.752728641324803</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.298</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.332</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.357</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.374</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.411</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.455</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.507</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.563</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.501</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.484</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2.515</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.538</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.498</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.018</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.058</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.087</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.093</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.105</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.175</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.222</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.271</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.202</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.189</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.214</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.231</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.221</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.196</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3796.818</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3824.68</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3846.687</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3838.259</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3860.534</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3900.848</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3971.21</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>4053.846</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>4138.324</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3979.886</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3974.002</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>4028.196</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>4031.242</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>3986.833</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>3963.49</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3283.9</t>
+          <t>6774069639.21388</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3327.2</t>
+          <t>6585749239.32306</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>6632339257.63202</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>7144374651.09527</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3388.2</t>
+          <t>7371615224.73656</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3427.8</t>
+          <t>7597379565.89764</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3483.1</t>
+          <t>7880155485.86231</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3561.4</t>
+          <t>7948632296.80047</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3636.5</t>
+          <t>8583959741.32965</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3472.1</t>
+          <t>6451246111.01363</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3473.5</t>
+          <t>6384001353.92694</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3518.6</t>
+          <t>6709810435.58911</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3522.5</t>
+          <t>6569463081.19678</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3495.3</t>
+          <t>6339867550.78732</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>6105088738.01219</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1842113949.99015</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1831772662.09415</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1925184755.28565</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2138215003.83796</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2274044536.89226</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2359438587.27575</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2323661246.88211</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2327277415.93118</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2457815972.18401</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2156985231.37454</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1942297781.03994</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1888126100.42442</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1989669722.99643</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2029776522.55925</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1910627624.85825</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1428810.57725751</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1411657.37137976</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1345537.97623085</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1202063.80674106</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1066308.62726811</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1050516.24753936</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>993366.517719069</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>844138.026429604</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>815755.457435788</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>764989.311424003</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>775159.589616688</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>692216.931731536</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>741700.165698943</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>720909.138011505</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>672571.362630279</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>17772.0258382872</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17597.6820755566</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>17628.6935184932</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>18970.7096592787</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>20991.0917492891</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>22693.9169648703</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>24386.0421147086</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>27962.6145098693</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>30822.705796979</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>26683.4629215542</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>29483.3384616855</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>31755.3732004784</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>30870.2189751297</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>30243.9169889227</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>30048.3494192898</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>55041.7962492808</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>53008.654163666</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>53704.0658855076</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>62958.1561040825</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>71819.1749149873</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>79472.244924884</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>87082.1477653738</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>99175.8416590771</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>116249.48034054</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>79506.9309663126</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>87166.1439166624</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>97291.7351180329</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>92813.3799667543</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>89480.6266765698</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>86566.1248732729</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.782680164827781</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.816382605140653</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.746325899771191</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.573274901710928</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.489944433819385</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.45280322975382</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.498970645860548</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.530285979497219</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.479565614820466</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.609700404757711</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.788345759289402</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.863540787455387</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.770394331927178</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.722012231963816</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.811970032756567</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>23081.3459039958</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>23656.6666647379</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>25029.7715820914</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>30705.7398797858</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>34981.5141766616</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>36457.9969003658</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>38314.6088594209</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>44729.2853098203</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>50804.8959451956</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>51360.171521322</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>49504.5875000285</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>52988.2014326513</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>51184.8404096611</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>54187.0837068835</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>55821.9442749734</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0827197921178</t>
+          <t>912.750941428081</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656989727557</t>
+          <t>889.94445032024</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296108291</t>
+          <t>922.376751286726</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016973125884</t>
+          <t>1021.74941646579</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923144947343</t>
+          <t>1080.20356113066</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793907242183</t>
+          <t>1102.43836430042</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431984708506</t>
+          <t>1068.49737751511</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660707770887</t>
+          <t>1047.28531002213</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990209409845</t>
+          <t>1082.07095719997</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694866647548</t>
+          <t>979.557325783169</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75431847325941</t>
+          <t>887.420743381891</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718390804597701</t>
+          <t>852.812150146533</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778331257783312</t>
+          <t>891.668783273475</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75295534974776</t>
+          <t>913.860934923797</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752728641324803</t>
+          <t>870.247153203483</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>3553227126.98786</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>3640160386.70775</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>3922490715.00675</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>4136010609.58881</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>4429036077.29594</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>4024032535.79942</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>4061358618.86671</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>4362219221.92445</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>4250092661.88267</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>3031610668.3363</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>2573048797.77341</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>2259963679.25059</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>2160885293.63874</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>2282200763.87171</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>2201612103.97148</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>4016598180.12121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>3932675858.38416</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>4210014194.8826</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>4576844546.68374</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>4808616478.69301</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>4562311841.48551</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>4603663391.61492</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>4791433976.83528</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>4867784187.44093</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>3646928182.86426</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>3294713280.41482</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>2975314639.85434</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>2883383302.0806</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>3019165936.37136</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>2942382719.27267</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>-463371053.133347</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>-292515471.67641</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>-287523479.87585</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>-440833937.094928</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>-379580401.397074</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>-538279305.686091</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>-542304772.748204</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>-429214754.910825</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>-617691525.558262</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>-615317514.527964</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-721664482.641404</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>-715350960.60375</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>-722498008.441859</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-736965172.499654</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>-740770615.301189</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>1627.14299871172</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>1616.47961910314</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>1610.77041011882</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>1607.49271276342</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>1609.4432832985</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>1601.62601626016</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>1601.64620407413</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>1602.64602646026</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>1600.99498106894</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>1576.79382379655</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>1587.01512313245</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>1589.25022583559</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>1578.60535986376</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>1573.67970825267</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>1576.86176269642</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1652.01144040313</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1640.36710912516</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1632.09612563332</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1626.2429687821</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>1626.4469261331</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>1618.20606065257</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>1617.86428715943</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>1617.07533679772</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>1614.82965085584</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>1591.31786713238</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>1599.96869109417</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>1601.34999258764</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>1588.60399903898</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>1582.32765368074</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1586.34787243071</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>50476.8599103353</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>49102.1615266963</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>52381.8696601114</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>61254.1006222511</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>73579.3463741429</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>78271.45467531</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>88403.8665835813</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>108909.527242304</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>124727.40237046</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>89637.1320387041</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>93725.6782135953</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>104742.431771004</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>98627.7783942823</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>102073.916928352</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>100453.268998073</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1776414247.06386</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1723809426.64526</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1761014015.88307</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1914275940.83951</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2021809662.62431</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2049113400.65554</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2167219411.99704</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2266770100.64055</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2405326127.55255</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1610144368.24041</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1675025791.61397</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1771013837.82261</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1756527100.65303</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1748148458.49879</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1678365962.86102</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>37012.6031454399</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35600.2378289728</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>38035.6631409049</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>47695.4366330738</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>58277.6334968709</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>66876.7984255897</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>75725.1963437071</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>91765.7105335162</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>108854.444006294</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>79709.0868678344</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>86324.1167520725</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>102060.151664664</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>97478.1049839443</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>99792.7409998766</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>97445.4727937867</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3796.818</t>
+          <t>3249400934.5048</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3824.68</t>
+          <t>3202448346.0831</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3846.687</t>
+          <t>3366942930.96966</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3838.259</t>
+          <t>3987382137.87799</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3860.534</t>
+          <t>4339286081.07609</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3900.848</t>
+          <t>4636370156.0741</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3971.21</t>
+          <t>4773485668.18694</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4053.846</t>
+          <t>4952312028.61535</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4138.324</t>
+          <t>5288892247.40036</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3979.886</t>
+          <t>3675261423.11732</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3974.002</t>
+          <t>3607966984.26313</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>4028.196</t>
+          <t>3810898248.84383</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4031.242</t>
+          <t>3822071069.2625</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>3986.833</t>
+          <t>3840121725.683</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3963.49</t>
+          <t>3631606086.21758</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3283.9</t>
+          <t>13464.2567648954</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3327.2</t>
+          <t>13501.9236977235</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>14346.2065192064</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>13558.6639891773</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3388.2</t>
+          <t>15301.7128772721</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3427.8</t>
+          <t>11394.6562497203</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3483.1</t>
+          <t>12678.6702398742</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3561.4</t>
+          <t>17143.8167087881</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3636.5</t>
+          <t>15872.9583641657</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3472.1</t>
+          <t>9928.04517086972</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>3473.5</t>
+          <t>7401.56146152289</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3518.6</t>
+          <t>2682.28010633992</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>3522.5</t>
+          <t>1149.67341033806</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3495.3</t>
+          <t>2281.17592847557</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3007.7962042865</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6786.705</t>
+          <t>-1472986687.44094</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6595.712</t>
+          <t>-1478638919.43784</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6638.788</t>
+          <t>-1605928915.08658</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7146.042</t>
+          <t>-2073106197.03849</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7374.652</t>
+          <t>-2317476418.45178</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7593.568</t>
+          <t>-2587256755.41856</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7872.528</t>
+          <t>-2606266256.1899</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7952.548</t>
+          <t>-2685541927.97481</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>8588.333</t>
+          <t>-2883566119.8478</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6449.92</t>
+          <t>-2065117054.87691</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6385.312</t>
+          <t>-1932941192.64917</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>6711.782</t>
+          <t>-2039884411.02122</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>6572.398</t>
+          <t>-2065543968.60946</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>6338.944</t>
+          <t>-2091973267.18421</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>6104.179</t>
+          <t>-1953240123.35656</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61794.3816</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>62644.5332</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>67020.3456</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>81025.5936</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>92476.5016</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>95716.0776</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>102347.7228</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>122012.874</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>132927.9624</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>111447.3096</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>111088.3572</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>119056.368</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>108570.7392</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>113909.8089</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>113759.455</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2187.228</t>
+          <t>0.0576961865556587</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2186.321</t>
+          <t>0.0608752497224689</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2177.107</t>
+          <t>0.0620301475275586</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2152.761</t>
+          <t>0.060311207738015</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2154.553</t>
+          <t>0.0628823615695941</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2169.491</t>
+          <t>0.0581449525317708</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2206.719</t>
+          <t>0.0569861083554905</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2241.116</t>
+          <t>0.0637308588204391</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2275.975</t>
+          <t>0.056840673584178</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2165.114</t>
+          <t>0.0337254838700353</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2159.344</t>
+          <t>0.0395900184151265</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2190.037</t>
+          <t>0.0396015559097463</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2185.038</t>
+          <t>0.0315792784857534</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2142.837</t>
+          <t>0.0313934703248104</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2119.164</t>
+          <t>0.0315612978835612</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>58700.3216</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>60157.452</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>65515.896</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>80279.0016</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>91966.5026</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>96766.098</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>102623.9548</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>118272.7795</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>135288.5964</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>126843.112</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>122499.9828</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>134784.576</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>128850.0224</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>134362.5489</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>134693.958</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1843.446</t>
+          <t>65601.9226</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1832.952</t>
+          <t>66958.36972</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1926.017</t>
+          <t>72750.6816</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2138.507</t>
+          <t>89063.22208</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2274.257</t>
+          <t>101970.81713</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2359.41</t>
+          <t>107187.79929</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2322.895</t>
+          <t>114067.36764</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2327.873</t>
+          <t>131277.59105</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2458.297</t>
+          <t>150171.03328</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2156.823</t>
+          <t>141714.88804</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1942.533</t>
+          <t>136917.36801</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1888.515</t>
+          <t>150847.4208</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1990.027</t>
+          <t>144301.92656</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2029.671</t>
+          <t>150139.71285</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1910.456</t>
+          <t>151070.3775</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>78.14</t>
+          <t>371077.5428</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>81.52</t>
+          <t>381527.3912</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>74.56</t>
+          <t>405728.592</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>494505.2112</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>566792.9862</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>602515.1418</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>641462.1836</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>52.99</t>
+          <t>757575.3965</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>873103.65</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>60.98</t>
+          <t>823968.3364</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>78.81</t>
+          <t>770120.3412</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>86.32</t>
+          <t>844318.992</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>77.01</t>
+          <t>824420.1856</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>72.21</t>
+          <t>869707.6131</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>81.21</t>
+          <t>882057.575</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>84253.2719221916</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>84680.041765017</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>85805.7711519783</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>86289.1275311529</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t>87654.1099233288</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>90033.5703355483</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>93500.8552660246</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>95189.2762684075</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>97309.7069418454</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>94038.898681727</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>95388.76148</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>97594.4229359933</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>97540.7732856739</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>95894.2003743835</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>94679.9712736618</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>75623.1074265767</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>76356.3540815593</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77460.3807649418</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>78002.4162152906</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>79296.1263673239</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>81447.2736976534</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>83865.0311569449</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>85774.4449453735</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>87670.8580673781</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>84014.2118586045</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>85344.3344</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>87109.2722403797</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>87238.6342595876</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>86013.8087786541</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>84472.7202545982</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>44491.10504</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>46882.24188</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>50197.176</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>60529.9464</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>70622.79567</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>71491.21122</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>74869.04236</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>93010.21595</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>100432.69552</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>79148.90236</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>79993.66599</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>86424.5472</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>77219.43504</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>81490.22385</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>83660.82615</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3283900000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3327200000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3.362e+09</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3.364e+09</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3388200000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3427800000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3483100000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3561400000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3636500000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3472100000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3473500000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3518600000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3522500000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3495300000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>3.462e+09</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3796817893.47852</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3824679951.63623</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3846687358.50518</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3838258654.91951</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3860534423.86954</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3900847529.80908</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3971209679.26154</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4053846161.8182</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>4138323946.24825</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3979885985.69808</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3974002234.9397</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>4028195906.3542</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>4031241507.96132</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3986832756.21399</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3963490159.26814</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2187227686.27012</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2186320765.38144</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2177106596.22547</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2152760906.44989</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2154553456.03826</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2169490759.72431</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2206718695.85078</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2241115750.34752</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2275974609.99444</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2165114214.68387</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2159343802.53922</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2190037357.52169</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2185038018.63716</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2142837338.63236</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2119164279.37738</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2298300</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2331600</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2356900</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2360200</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2373600</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2410600</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2454600</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2506900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2562700</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2501000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2483800</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2515500</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2537600</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2519600</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2498500</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2018200</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2058300</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2087200</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2092700</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2105200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2140200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2174700</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2222200</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2271400</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2202000</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2188700</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2214000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2231400</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2221100</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2195500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3796817893.47852</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3824679951.63623</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3846687358.50518</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3838258654.91951</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3860534423.86954</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3900847529.80908</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3971209679.26154</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4053846161.8182</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4138323946.24825</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3979885985.69808</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3974002234.9397</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>4028195906.3542</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>4031241507.96132</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>3986832756.21399</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3963490159.26814</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3283900000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3327200000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3.362e+09</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3.364e+09</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3388200000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3427800000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3483100000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3561400000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3636500000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3472100000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>3473500000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3518600000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>3522500000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>3495300000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>3.462e+09</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>236980.0588</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>236684.69</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>254773.008</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>311602.6144</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>362604.3134</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>383159.1621</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>417431.7536</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>492128.7335</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>556474.2384</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>472521.9752</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>471053.0268</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>529475.04</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>496080.552</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>511779.3507</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>513657.8825</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>110093.12</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>113840.6116</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>122947.8576</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>149593.2816</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>172593.6128</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>178678.8861</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>188936.41</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>224287.807</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>250603.7288</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>220863.7904</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>216911.034</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>237271.968</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>221521.3616</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>231629.9367</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>234731.3365</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>480104.050288074</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>492680.27474209</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>484751.721399393</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>482873.345341069</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>493233.213072097</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>514446.732043037</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>529454.030005568</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>556406.928767323</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>572636.041643485</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>562013.51326567</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>536534.0176</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>542321.123427101</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>558274.605905168</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>555662.806521576</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>555061.563523521</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
